--- a/docs/platform/p1-kit/boards/board-03-goal.xlsx
+++ b/docs/platform/p1-kit/boards/board-03-goal.xlsx
@@ -9,8 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="段階" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="週の記録" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="前提" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="記録" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="ボード" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -23,33 +23,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">③ 現在地ボード：目標達成ロードマップ</t>
   </si>
   <si>
-    <t xml:space="preserve">「段階」シートに初回の計画書のマイルストーンを転記し、達成したら「状態」を「達成」にしてください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「週の記録」シートに毎週の予定時間と実績時間を入れてください。2週続けて7割未満なら計画の量を減らす目安です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「ボード」シートで、今どの段階にいるかと進み具合が分かります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色のセル＝あなたが入力する欄（青字）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白いセル＝自動計算（触らない）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毎月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -59,33 +48,191 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">行目の数字は記入例（架空）です。上書きしてお使いください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">このシートは目安を可視化するもので、結果を保証するものではありません。氏名・口座番号・ID・パスワードなどは書かないでください。</t>
+      <t xml:space="preserve">回、「記録」シートの「実績」に、その月までの累計の取り組み時間（勉強時間など）を入れてください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入れると、現在地・進み具合・必要なペース・期限内に届く見込みが自動で計算され、残りの月の予定と、各段階に到達する見込みの時期が作り直されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「前提」と「段階」は初回の計画書から転記します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凡例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">前提（初回の計画書から転記）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計の取り組み時間：最初の値（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計の取り組み時間：目標の値（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期限までの月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実績（時間）※入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新後の予定（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースが続いた場合（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 入力するのは「実績」の列だけです。月ごとに上から順に入れてください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地ボード：目標達成ロードマップ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記録した月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在の累計の取り組み時間（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標までの進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画と比べて</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残りの月数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標に届くために必要な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月あたりの変化（時間）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">これまでの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月あたりの平均の変化（時間）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースで目標に届く見込み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">これからの予定（自動更新）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「記録」シートの「更新後の予定」列に、残りの月ごとに目指す値が自動で入ります。実績を入れるたびに作り直されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">段階（マイルストーン）の見込み</t>
   </si>
   <si>
     <t xml:space="preserve">段階</t>
   </si>
   <si>
-    <t xml:space="preserve">内容</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目安の時期</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状態（未着手／進行中／達成）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商業簿記の基礎</t>
+    <t xml:space="preserve">到達の目安（累計時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースで到達する見込み</t>
   </si>
   <si>
     <r>
@@ -96,7 +243,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">M1 </t>
     </r>
     <r>
       <rPr>
@@ -105,17 +252,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">達成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工業簿記</t>
+      <t xml:space="preserve">商業簿記の基礎</t>
+    </r>
   </si>
   <si>
     <r>
@@ -126,7 +264,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">M2 </t>
     </r>
     <r>
       <rPr>
@@ -135,17 +273,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">進行中</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">過去問演習</t>
+      <t xml:space="preserve">工業簿記</t>
+    </r>
   </si>
   <si>
     <r>
@@ -156,7 +285,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t xml:space="preserve">M3 </t>
     </r>
     <r>
       <rPr>
@@ -165,266 +294,55 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">未着手</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゴール</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">過去問演習</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ゴール 受験</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 架空の記入例（簿記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月の試験で合格基準に届く力をつける</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">級、合計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 架空の記入例（簿記2級）です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">週</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予定時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実績時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">達成率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">判定</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週目</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 架空の記入例です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在地ボード：目標達成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">段階の数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">達成した段階</t>
-  </si>
-  <si>
-    <t xml:space="preserve">進み具合</t>
-  </si>
-  <si>
-    <t xml:space="preserve">今いる段階</t>
-  </si>
-  <si>
-    <t xml:space="preserve">直近の週の達成率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">計画を見直す目安</t>
+      <t xml:space="preserve">時間と仮定）。段階と目安は初回の計画書から転記します。</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -433,10 +351,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,13 +382,16 @@
       <sz val="14"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -478,25 +399,10 @@
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -508,12 +414,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -532,8 +433,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,13 +451,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE6F5"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -602,60 +516,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -687,7 +605,7 @@
       <rgbColor rgb="FFBBBBBB"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFC0504D"/>
+      <rgbColor rgb="FFBE4B48"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFDDE6F5"/>
       <rgbColor rgb="FF660066"/>
@@ -704,7 +622,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -712,11 +630,11 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF4A7EBB"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -757,7 +675,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>週ごとの予定と実績（時間）</a:t>
+              <a:t>当初の計画・実績・更新後の予定</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -772,55 +690,55 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>週の記録!B1</c:f>
+              <c:f>記録!B1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>予定時間</c:v>
+                  <c:v>当初の計画（時間）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4a7ebb"/>
             </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -830,115 +748,111 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>週の記録!$A$2:$A$9</c:f>
+              <c:f>記録!$A$2:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1週目</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2週目</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3週目</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4週目</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5週目</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6週目</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7週目</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8週目</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>週の記録!$B$2:$B$9</c:f>
+              <c:f>記録!$B$2:$B$8</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>35.7142857142857</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9</c:v>
+                  <c:v>71.4285714285714</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>107.142857142857</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9</c:v>
+                  <c:v>142.857142857143</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9</c:v>
+                  <c:v>178.571428571429</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9</c:v>
+                  <c:v>214.285714285714</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>週の記録!C1</c:f>
+              <c:f>記録!C1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>実績時間</c:v>
+                  <c:v>実績（時間）※入力</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c0504d"/>
+              <a:srgbClr val="be4b48"/>
             </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -948,71 +862,177 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>週の記録!$A$2:$A$9</c:f>
+              <c:f>記録!$A$2:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1週目</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2週目</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3週目</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4週目</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5週目</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6週目</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7週目</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8週目</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>週の記録!$C$2:$C$9</c:f>
+              <c:f>記録!$C$2:$C$8</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
         </c:ser>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="86996598"/>
-        <c:axId val="76163747"/>
-      </c:barChart>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>記録!D1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>更新後の予定（時間）</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$D$2:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="3">
+                  <c:v>122.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="19877224"/>
+        <c:axId val="78700483"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="86996598"/>
+        <c:axId val="19877224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1038,7 +1058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76163747"/>
+        <c:crossAx val="78700483"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1046,7 +1066,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76163747"/>
+        <c:axId val="78700483"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1062,7 +1082,41 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>時間</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1088,7 +1142,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86996598"/>
+        <c:crossAx val="19877224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1144,16 +1198,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>133560</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>160560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>181440</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1161,8 +1215,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="1895760"/>
-        <a:ext cx="6479280" cy="2878920"/>
+        <a:off x="9492480" y="380880"/>
+        <a:ext cx="7199640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1355,55 +1409,60 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1422,88 +1481,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="7" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="B2" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="B3" s="7" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
+      <c r="B4" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1522,179 +1533,166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
+        <v>35.7142857142857</v>
+      </c>
+      <c r="C2" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10" t="n">
-        <f aca="false">IF(C2="","",C2/B2)</f>
-        <v>0.888888888888889</v>
-      </c>
-      <c r="E2" s="11" t="str">
-        <f aca="false">IF(D2="","",IF(D2&lt;0.7,"7割未満","OK"))</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>35</v>
+      <c r="D2" s="9" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4))</f>
+        <v/>
+      </c>
+      <c r="E2" s="9" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" s="9" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
+        <v>71.4285714285714</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4))</f>
+        <v/>
+      </c>
+      <c r="E3" s="9" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
+        <v>107.142857142857</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4))</f>
+        <v/>
+      </c>
+      <c r="E4" s="9" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
+        <v>142.857142857143</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4))</f>
+        <v>122.5</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4))</f>
+        <v>106.666666666667</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
+        <v>178.571428571429</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4))</f>
+        <v>165</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4))</f>
+        <v>133.333333333333</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="10" t="n">
-        <f aca="false">IF(C3="","",C3/B3)</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="E3" s="11" t="str">
-        <f aca="false">IF(D3="","",IF(D3&lt;0.7,"7割未満","OK"))</f>
-        <v>7割未満</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <f aca="false">IF(C4="","",C4/B4)</f>
-        <v>0.555555555555556</v>
-      </c>
-      <c r="E4" s="11" t="str">
-        <f aca="false">IF(D4="","",IF(D4&lt;0.7,"7割未満","OK"))</f>
-        <v>7割未満</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <f aca="false">IF(C5="","",C5/B5)</f>
-        <v>0.888888888888889</v>
-      </c>
-      <c r="E5" s="11" t="str">
-        <f aca="false">IF(D5="","",IF(D5&lt;0.7,"7割未満","OK"))</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10" t="str">
-        <f aca="false">IF(C6="","",C6/B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="11" t="str">
-        <f aca="false">IF(D6="","",IF(D6&lt;0.7,"7割未満","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="B7" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7/B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="11" t="str">
-        <f aca="false">IF(D7="","",IF(D7&lt;0.7,"7割未満","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>40</v>
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
+        <v>214.285714285714</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4))</f>
+        <v>207.5</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4))</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10" t="str">
-        <f aca="false">IF(C8="","",C8/B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="11" t="str">
-        <f aca="false">IF(D8="","",IF(D8&lt;0.7,"7割未満","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10" t="str">
-        <f aca="false">IF(C9="","",C9/B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="11" t="str">
-        <f aca="false">IF(D9="","",IF(D9&lt;0.7,"7割未満","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>42</v>
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A8/前提!$B$4</f>
+        <v>250</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4))</f>
+        <v>250</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A8-ボード!$B$4))</f>
+        <v>186.666666666667</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1713,70 +1711,202 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="13" t="n">
-        <f aca="false">COUNTA(段階!A2:A6)</f>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <f aca="false">IF(COUNT(記録!C2:C8)=0,"",COUNT(記録!C2:C8))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="10" t="n">
+        <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C8&lt;&gt;""),記録!C2:C8))</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">前提!B3</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <f aca="false">IFERROR((B5-前提!B2)/(前提!B3-前提!B2),"")</f>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="12" t="str">
+        <f aca="false">IF(B4="","",IF((B5-INDEX(記録!B2:B8,B4))*SIGN(前提!B3-前提!B2)&gt;=0,"計画どおり、または先行","計画より遅れ"))</f>
+        <v>計画より遅れ</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="13" t="n">
-        <f aca="false">COUNTIF(段階!D2:D6,"達成")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="10" t="n">
-        <f aca="false">IFERROR(B4/B3,"")</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="11" t="str">
-        <f aca="false">IFERROR(INDEX(段階!A2:A6,MATCH("進行中",段階!D2:D6,0)),"—")</f>
-        <v>M2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(週の記録!D2:D9&lt;&gt;""),週の記録!D2:D9),"")</f>
-        <v>0.888888888888889</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="11" t="str">
-        <f aca="false">IF(SUMPRODUCT((週の記録!E2:E8="7割未満")*(週の記録!E3:E9="7割未満"))&gt;0,"7割未満が2週続いた：量を減らすか期限の見直しを検討","このままでOK")</f>
-        <v>7割未満が2週続いた：量を減らすか期限の見直しを検討</v>
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <f aca="false">IFERROR(IF(B9&lt;=0,"",(前提!B3-B5)/B9),"")</f>
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <f aca="false">IFERROR((B5-前提!B2)/B4,"")</f>
+        <v>26.6666666666667</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="12" t="str">
+        <f aca="false">IFERROR(IF((前提!B3-B5)*SIGN(前提!B3-前提!B2)&lt;=0,"達成済み",IF(B11*SIGN(前提!B3-前提!B2)&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）"))),"")</f>
+        <v>期限より遅れる（10か月目ごろ）</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="12" t="str">
+        <f aca="false">IF(B$5="","",IF(B$5&gt;=B19,"達成","未達成"))</f>
+        <v>達成</v>
+      </c>
+      <c r="D19" s="12" t="str">
+        <f aca="false">IFERROR(IF(B$5&gt;=B19,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B19-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C20" s="12" t="str">
+        <f aca="false">IF(B$5="","",IF(B$5&gt;=B20,"達成","未達成"))</f>
+        <v>未達成</v>
+      </c>
+      <c r="D20" s="12" t="str">
+        <f aca="false">IFERROR(IF(B$5&gt;=B20,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B20-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
+        <v>5か月目ごろ</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="C21" s="12" t="str">
+        <f aca="false">IF(B$5="","",IF(B$5&gt;=B21,"達成","未達成"))</f>
+        <v>未達成</v>
+      </c>
+      <c r="D21" s="12" t="str">
+        <f aca="false">IFERROR(IF(B$5&gt;=B21,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B21-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
+        <v>8か月目ごろ</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f aca="false">IF(B$5="","",IF(B$5&gt;=B22,"達成","未達成"))</f>
+        <v>未達成</v>
+      </c>
+      <c r="D22" s="12" t="str">
+        <f aca="false">IFERROR(IF(B$5&gt;=B22,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B22-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
+        <v>10か月目ごろ</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-03-goal.xlsx
+++ b/docs/platform/p1-kit/boards/board-03-goal.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">③ 現在地ボード：目標達成ロードマップ</t>
   </si>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">現在地</t>
   </si>
   <si>
-    <t xml:space="preserve">記録した月数</t>
+    <t xml:space="preserve">最後に実績を入れた月</t>
   </si>
   <si>
     <t xml:space="preserve">現在の累計の取り組み時間（時間）</t>
@@ -211,7 +211,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">今のペースで目標に届く見込み</t>
+    <t xml:space="preserve">今のペースで目標に届く見込み（過去の数値を直線で延ばした参考計算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力のチェック</t>
   </si>
   <si>
     <t xml:space="preserve">これからの予定（自動更新）</t>
@@ -516,7 +519,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -566,6 +569,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1022,11 +1029,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="19877224"/>
-        <c:axId val="78700483"/>
+        <c:axId val="23359613"/>
+        <c:axId val="3088272"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="19877224"/>
+        <c:axId val="23359613"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1058,7 +1065,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78700483"/>
+        <c:crossAx val="3088272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1066,7 +1073,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78700483"/>
+        <c:axId val="3088272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1142,7 +1149,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19877224"/>
+        <c:crossAx val="23359613"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1206,8 +1213,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>98280</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>62640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1518,6 +1525,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1570,11 +1583,11 @@
         <v>30</v>
       </c>
       <c r="D2" s="9" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
       <c r="E2" s="9" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
@@ -1590,11 +1603,11 @@
         <v>55</v>
       </c>
       <c r="D3" s="9" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
       <c r="E3" s="9" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
@@ -1610,11 +1623,11 @@
         <v>80</v>
       </c>
       <c r="D4" s="9" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
       <c r="E4" s="9" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
@@ -1628,11 +1641,11 @@
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
         <v>122.5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
         <v>106.666666666667</v>
       </c>
     </row>
@@ -1646,11 +1659,11 @@
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
         <v>165</v>
       </c>
       <c r="E6" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
         <v>133.333333333333</v>
       </c>
     </row>
@@ -1664,11 +1677,11 @@
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
         <v>207.5</v>
       </c>
       <c r="E7" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
         <v>160</v>
       </c>
     </row>
@@ -1682,11 +1695,11 @@
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4)),"")</f>
         <v>250</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A8-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A8-ボード!$B$4)),"")</f>
         <v>186.666666666667</v>
       </c>
     </row>
@@ -1696,6 +1709,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C8" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1711,7 +1730,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1735,7 +1754,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="9" t="n">
-        <f aca="false">IF(COUNT(記録!C2:C8)=0,"",COUNT(記録!C2:C8))</f>
+        <f aca="false">IF(COUNT(記録!C2:C8)=0,"",LOOKUP(2,1/(記録!C2:C8&lt;&gt;""),記録!A2:A8))</f>
         <v>3</v>
       </c>
     </row>
@@ -1762,7 +1781,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="11" t="n">
-        <f aca="false">IFERROR((B5-前提!B2)/(前提!B3-前提!B2),"")</f>
+        <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.32</v>
       </c>
     </row>
@@ -1771,7 +1790,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="12" t="str">
-        <f aca="false">IF(B4="","",IF((B5-INDEX(記録!B2:B8,B4))*SIGN(前提!B3-前提!B2)&gt;=0,"計画どおり、または先行","計画より遅れ"))</f>
+        <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((B5-INDEX(記録!B2:B8,B4))*SIGN((前提!B3-前提!B2))&gt;=0,"計画どおり、または先行","計画より遅れ")))</f>
         <v>計画より遅れ</v>
       </c>
     </row>
@@ -1789,7 +1808,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="10" t="n">
-        <f aca="false">IFERROR(IF(B9&lt;=0,"",(前提!B3-B5)/B9),"")</f>
+        <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,0,IF(B9&lt;=0,"",(前提!B3-B5)/B9)))</f>
         <v>42.5</v>
       </c>
     </row>
@@ -1798,94 +1817,87 @@
         <v>29</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">IFERROR((B5-前提!B2)/B4,"")</f>
+        <f aca="false">IF(COUNT(記録!C2:C8)&lt;2,"",(B5-前提!B2)/B4)</f>
         <v>26.6666666666667</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="12" t="str">
-        <f aca="false">IFERROR(IF((前提!B3-B5)*SIGN(前提!B3-前提!B2)&lt;=0,"達成済み",IF(B11*SIGN(前提!B3-前提!B2)&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）"))),"")</f>
+        <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,"達成済み",IF(B9&lt;=0,"期限を過ぎています（前提の見直しが必要）",IF(COUNT(記録!C2:C8)&lt;2,"記録が2か月分以上で表示",IF(B11*SIGN((前提!B3-前提!B2))&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）")))))))</f>
         <v>期限より遅れる（10か月目ごろ）</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
+      <c r="B13" s="13" t="str">
+        <f aca="false">IF(COUNTIF(記録!C2:C8,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(COUNT(記録!C2:C8)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK")))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="8" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="C19" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="D19" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="7" t="n">
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="n">
         <v>60</v>
-      </c>
-      <c r="C19" s="12" t="str">
-        <f aca="false">IF(B$5="","",IF(B$5&gt;=B19,"達成","未達成"))</f>
-        <v>達成</v>
-      </c>
-      <c r="D19" s="12" t="str">
-        <f aca="false">IFERROR(IF(B$5&gt;=B19,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B19-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>130</v>
       </c>
       <c r="C20" s="12" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B20,"達成","未達成"))</f>
-        <v>未達成</v>
+        <v>達成</v>
       </c>
       <c r="D20" s="12" t="str">
-        <f aca="false">IFERROR(IF(B$5&gt;=B20,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B20-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
-        <v>5か月目ごろ</v>
+        <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B20,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B20-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
+        <v>—</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="C21" s="12" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B21,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
       <c r="D21" s="12" t="str">
-        <f aca="false">IFERROR(IF(B$5&gt;=B21,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B21-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
-        <v>8か月目ごろ</v>
+        <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B21,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B21-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
+        <v>5か月目ごろ</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1893,23 +1905,45 @@
         <v>41</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C22" s="12" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B22,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
       <c r="D22" s="12" t="str">
-        <f aca="false">IFERROR(IF(B$5&gt;=B22,"—",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B22-B$5)/B$11,0)&amp;"か月目ごろ")),"")</f>
+        <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B22,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B22-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
+        <v>8か月目ごろ</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="C23" s="12" t="str">
+        <f aca="false">IF(B$5="","",IF(B$5&gt;=B23,"達成","未達成"))</f>
+        <v>未達成</v>
+      </c>
+      <c r="D23" s="12" t="str">
+        <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B23,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B23-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>10か月目ごろ</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>42</v>
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B20:B23" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/platform/p1-kit/boards/board-03-goal.xlsx
+++ b/docs/platform/p1-kit/boards/board-03-goal.xlsx
@@ -8,10 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="前提" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="記録" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ボード" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="スマホ" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="使い方" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="前提" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="記録" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="ボード" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,9 +24,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
-  <si>
-    <t xml:space="preserve">③ 現在地ボード：目標達成ロードマップ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+  <si>
+    <t xml:space="preserve">③ スマホで見る：目標達成ロードマップ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計画と比べて</t>
   </si>
   <si>
     <r>
@@ -34,7 +50,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">毎月</t>
+      <t xml:space="preserve">必要なペース（</t>
     </r>
     <r>
       <rPr>
@@ -51,39 +67,22 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回、「記録」シートの「実績」に、その月までの累計の取り組み時間（勉強時間など）を入れてください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">入れると、現在地・進み具合・必要なペース・期限内に届く見込みが自動で計算され、残りの月の予定と、各段階に到達する見込みの時期が作り直されます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「前提」と「段階」は初回の計画書から転記します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
-    </r>
+      <t xml:space="preserve">か月あたり）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">見込み（参考計算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力のチェック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">単位：時間。見込みは過去の数値を直線で延ばした参考計算です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 毎月の数字を入れる：累計の取り組み時間（時間）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -91,7 +90,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ID</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -99,72 +98,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">前提（初回の計画書から転記）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計の取り組み時間：最初の値（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計の取り組み時間：目標の値（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">期限までの月数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当初の計画（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実績（時間）※入力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">更新後の予定（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">今のペースが続いた場合（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 入力するのは「実績」の列だけです。月ごとに上から順に入れてください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在地ボード：目標達成ロードマップ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在地</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最後に実績を入れた月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在の累計の取り組み時間（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目標（時間）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目標までの進み具合</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当初の計画と比べて</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残りの月数</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標に届くために必要な</t>
-    </r>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -172,7 +109,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -180,18 +117,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">か月あたりの変化（時間）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">これまでの</t>
-    </r>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -199,7 +128,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -207,14 +136,273 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 段階ごとの見込み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 現在地ボード：目標達成ロードマップ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毎月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回、「スマホ」シートの下にある「毎月の数字を入れる」欄に、その月までの累計の取り組み時間（勉強時間など）を入れてください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入れると、現在地・進み具合・必要なペース・期限内に届く見込みが自動で計算され、残りの月の予定と、各段階に到達する見込みの時期が作り直されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「前提」と「段階」は初回の計画書から転記します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凡例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">前提（初回の計画書から転記）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計の取り組み時間：最初の値（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計の取り組み時間：目標の値（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期限までの月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実績（時間）※スマホのシートから自動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新後の予定（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースが続いた場合（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 実績は「スマホ」シートで入力します（この列は自動）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地ボード：目標達成ロードマップ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最後に実績を入れた月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在の累計の取り組み時間（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標（時間）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標までの進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画と比べて</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残りの月数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標に届くために必要な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月あたりの変化（時間）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">これまでの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">か月あたりの平均の変化（時間）</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">今のペースで目標に届く見込み（過去の数値を直線で延ばした参考計算）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入力のチェック</t>
   </si>
   <si>
     <t xml:space="preserve">これからの予定（自動更新）</t>
@@ -357,7 +545,7 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,7 +570,13 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="13"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -392,33 +586,26 @@
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -443,6 +630,18 @@
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -453,14 +652,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFDDE6F5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -519,68 +718,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -682,7 +909,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>当初の計画・実績・更新後の予定</a:t>
+              <a:t>計画・実績・予定</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -705,11 +932,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!B1</c:f>
+              <c:f>"当初の計画"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>当初の計画（時間）</c:v>
+                  <c:v>当初の計画</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -819,11 +1046,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!C1</c:f>
+              <c:f>"実績"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>実績（時間）※入力</c:v>
+                  <c:v>実績</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -898,7 +1125,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>記録!$C$2:$C$8</c:f>
+              <c:f>スマホ!$B$27:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -921,11 +1148,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!D1</c:f>
+              <c:f>"更新後の予定"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>更新後の予定（時間）</c:v>
+                  <c:v>更新後の予定</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1029,11 +1256,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="23359613"/>
-        <c:axId val="3088272"/>
+        <c:axId val="4613234"/>
+        <c:axId val="42997248"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="23359613"/>
+        <c:axId val="4613234"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1065,7 +1292,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3088272"/>
+        <c:crossAx val="42997248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1073,7 +1300,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3088272"/>
+        <c:axId val="42997248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1149,7 +1376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23359613"/>
+        <c:crossAx val="4613234"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1161,7 +1388,552 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>当初の計画・実績・更新後の予定</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"当初の計画"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>当初の計画</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>35.7142857142857</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.4285714285714</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>107.142857142857</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>142.857142857143</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>178.571428571429</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>214.285714285714</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"実績"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>実績</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$B$27:$B$33</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"更新後の予定"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>更新後の予定</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$D$2:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="3">
+                  <c:v>122.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="39087242"/>
+        <c:axId val="28342660"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="39087242"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="28342660"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="28342660"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>時間</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="39087242"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1205,6 +1977,41 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>356400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>129600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>75600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="5143680"/>
+        <a:ext cx="3419640" cy="2519640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -1218,7 +2025,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1416,63 +2223,200 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="3" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B3" s="4" t="n">
+        <f aca="false">ボード!B5</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="n">
+        <f aca="false">ボード!B6</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <f aca="false">ボード!B7</f>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f aca="false">ボード!B8</f>
+        <v>計画より遅れ</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="B7" s="5" t="n">
+        <f aca="false">ボード!B10</f>
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="B8" s="7" t="str">
+        <f aca="false">ボード!B12</f>
+        <v>期限より遅れる（10か月目ごろ）</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="B9" s="3" t="str">
+        <f aca="false">ボード!B13</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="B10" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="str">
+        <f aca="false">ボード!A20</f>
+        <v>M1 商業簿記の基礎</v>
+      </c>
+      <c r="B37" s="3" t="str">
+        <f aca="false">IF(ボード!C20="達成","達成",ボード!D20)</f>
+        <v>達成</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="str">
+        <f aca="false">ボード!A21</f>
+        <v>M2 工業簿記</v>
+      </c>
+      <c r="B38" s="3" t="str">
+        <f aca="false">IF(ボード!C21="達成","達成",ボード!D21)</f>
+        <v>5か月目ごろ</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="str">
+        <f aca="false">ボード!A22</f>
+        <v>M3 過去問演習</v>
+      </c>
+      <c r="B39" s="3" t="str">
+        <f aca="false">IF(ボード!C22="達成","達成",ボード!D22)</f>
+        <v>8か月目ごろ</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="str">
+        <f aca="false">ボード!A23</f>
+        <v>ゴール 受験</v>
+      </c>
+      <c r="B40" s="3" t="str">
+        <f aca="false">IF(ボード!C23="達成","達成",ボード!D23)</f>
+        <v>10か月目ごろ</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27:B33" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1480,6 +2424,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1488,49 +2433,63 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>0</v>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>7</v>
+      <c r="A3" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1546,171 +2505,45 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
-        <v>35.7142857142857</v>
-      </c>
-      <c r="C2" s="7" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="9" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="9" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
-        <v>71.4285714285714</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-      <c r="E3" s="9" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
-        <v>107.142857142857</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="D4" s="9" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-      <c r="E4" s="9" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
-        <v>142.857142857143</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
-        <v>122.5</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
-        <v>106.666666666667</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
-        <v>178.571428571429</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
-        <v>165</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
-        <v>133.333333333333</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
-        <v>214.285714285714</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
-        <v>207.5</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="B2" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="10" t="n">
         <v>7</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A8/前提!$B$4</f>
-        <v>250</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4)),"")</f>
-        <v>250</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A8-ボード!$B$4)),"")</f>
-        <v>186.666666666667</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C8" type="decimal">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1730,6 +2563,199 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
+        <v>35.7142857142857</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
+        <v>30</v>
+      </c>
+      <c r="D2" s="16" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+      <c r="E2" s="16" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
+        <v>71.4285714285714</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
+        <v>55</v>
+      </c>
+      <c r="D3" s="16" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="16" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
+        <v>107.142857142857</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
+        <v>80</v>
+      </c>
+      <c r="D4" s="16" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="16" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
+        <v>142.857142857143</v>
+      </c>
+      <c r="C5" s="16" t="str">
+        <f aca="false">IF(スマホ!B30="","",スマホ!B30)</f>
+        <v/>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
+        <v>122.5</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
+        <v>106.666666666667</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
+        <v>178.571428571429</v>
+      </c>
+      <c r="C6" s="16" t="str">
+        <f aca="false">IF(スマホ!B31="","",スマホ!B31)</f>
+        <v/>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
+        <v>165</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
+        <v>133.333333333333</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
+        <v>214.285714285714</v>
+      </c>
+      <c r="C7" s="16" t="str">
+        <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
+        <v/>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
+        <v>207.5</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A8/前提!$B$4</f>
+        <v>250</v>
+      </c>
+      <c r="C8" s="16" t="str">
+        <f aca="false">IF(スマホ!B33="","",スマホ!B33)</f>
+        <v/>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4)),"")</f>
+        <v>250</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A8-ボード!$B$4)),"")</f>
+        <v>186.666666666667</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1740,201 +2766,201 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
+      <c r="A1" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>21</v>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="9" t="n">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="16" t="n">
         <f aca="false">IF(COUNT(記録!C2:C8)=0,"",LOOKUP(2,1/(記録!C2:C8&lt;&gt;""),記録!A2:A8))</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="17" t="n">
         <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C8&lt;&gt;""),記録!C2:C8))</f>
         <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="16" t="n">
         <f aca="false">前提!B3</f>
         <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="11" t="n">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="18" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="12" t="str">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="19" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((B5-INDEX(記録!B2:B8,B4))*SIGN((前提!B3-前提!B2))&gt;=0,"計画どおり、または先行","計画より遅れ")))</f>
         <v>計画より遅れ</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="17" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,0,IF(B9&lt;=0,"",(前提!B3-B5)/B9)))</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="9" t="n">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="16" t="n">
         <f aca="false">IF(COUNT(記録!C2:C8)&lt;2,"",(B5-前提!B2)/B4)</f>
         <v>26.6666666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="12" t="str">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="19" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,"達成済み",IF(B9&lt;=0,"期限を過ぎています（前提の見直しが必要）",IF(COUNT(記録!C2:C8)&lt;2,"記録が2か月分以上で表示",IF(B11*SIGN((前提!B3-前提!B2))&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）")))))))</f>
         <v>期限より遅れる（10か月目ごろ）</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="13" t="str">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="20" t="str">
         <f aca="false">IF(COUNTIF(記録!C2:C8,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(COUNT(記録!C2:C8)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK")))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
+      <c r="A15" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>33</v>
+      <c r="A16" s="12" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>34</v>
+      <c r="A18" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>38</v>
+      <c r="A19" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="n">
+      <c r="A20" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="C20" s="12" t="str">
+      <c r="C20" s="19" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B20,"達成","未達成"))</f>
         <v>達成</v>
       </c>
-      <c r="D20" s="12" t="str">
+      <c r="D20" s="19" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B20,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B20-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>—</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="n">
+      <c r="A21" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="10" t="n">
         <v>130</v>
       </c>
-      <c r="C21" s="12" t="str">
+      <c r="C21" s="19" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B21,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
-      <c r="D21" s="12" t="str">
+      <c r="D21" s="19" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B21,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B21-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>5か月目ごろ</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="7" t="n">
+      <c r="A22" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="C22" s="12" t="str">
+      <c r="C22" s="19" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B22,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
-      <c r="D22" s="12" t="str">
+      <c r="D22" s="19" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B22,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B22-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>8か月目ごろ</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="7" t="n">
+      <c r="A23" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="C23" s="12" t="str">
+      <c r="C23" s="19" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B23,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
-      <c r="D23" s="12" t="str">
+      <c r="D23" s="19" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B23,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B23-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>10か月目ごろ</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>43</v>
+      <c r="A25" s="12" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-03-goal.xlsx
+++ b/docs/platform/p1-kit/boards/board-03-goal.xlsx
@@ -1256,11 +1256,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4613234"/>
-        <c:axId val="42997248"/>
+        <c:axId val="58895846"/>
+        <c:axId val="48017189"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4613234"/>
+        <c:axId val="58895846"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1292,7 +1292,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42997248"/>
+        <c:crossAx val="48017189"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1300,7 +1300,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42997248"/>
+        <c:axId val="48017189"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1376,7 +1376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4613234"/>
+        <c:crossAx val="58895846"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1801,11 +1801,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="39087242"/>
-        <c:axId val="28342660"/>
+        <c:axId val="97271774"/>
+        <c:axId val="99881280"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39087242"/>
+        <c:axId val="97271774"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1837,7 +1837,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28342660"/>
+        <c:crossAx val="99881280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1845,7 +1845,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28342660"/>
+        <c:axId val="99881280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1921,7 +1921,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39087242"/>
+        <c:crossAx val="97271774"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2780,7 +2780,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="16" t="n">
-        <f aca="false">IF(COUNT(記録!C2:C8)=0,"",LOOKUP(2,1/(記録!C2:C8&lt;&gt;""),記録!A2:A8))</f>
+        <f aca="false">IF(COUNT(記録!C2:C8)=0,"",INDEX(記録!A2:A8,MATCH(9.99E+307,記録!C2:C8)))</f>
         <v>3</v>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="17" t="n">
-        <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C8&lt;&gt;""),記録!C2:C8))</f>
+        <f aca="false">IF(B4="","",INDEX(記録!C2:C8,MATCH(9.99E+307,記録!C2:C8)))</f>
         <v>80</v>
       </c>
     </row>

--- a/docs/platform/p1-kit/boards/board-03-goal.xlsx
+++ b/docs/platform/p1-kit/boards/board-03-goal.xlsx
@@ -718,7 +718,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -753,6 +753,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1256,11 +1260,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58895846"/>
-        <c:axId val="48017189"/>
+        <c:axId val="17262598"/>
+        <c:axId val="21236444"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58895846"/>
+        <c:axId val="17262598"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1292,7 +1296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48017189"/>
+        <c:crossAx val="21236444"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1300,7 +1304,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48017189"/>
+        <c:axId val="21236444"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1376,7 +1380,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58895846"/>
+        <c:crossAx val="17262598"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1801,11 +1805,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="97271774"/>
-        <c:axId val="99881280"/>
+        <c:axId val="46073092"/>
+        <c:axId val="36523450"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97271774"/>
+        <c:axId val="46073092"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1837,7 +1841,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99881280"/>
+        <c:crossAx val="36523450"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1845,7 +1849,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99881280"/>
+        <c:axId val="36523450"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1921,7 +1925,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97271774"/>
+        <c:crossAx val="46073092"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2310,57 +2314,58 @@
       <c r="B10" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="11" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="11" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="10"/>
+      <c r="B30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="10"/>
+      <c r="B33" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
@@ -2408,8 +2413,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27:B33" type="decimal">
@@ -2440,22 +2446,22 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2465,27 +2471,27 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2521,7 +2527,7 @@
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2529,7 +2535,7 @@
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2537,7 +2543,7 @@
       <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2572,171 +2578,171 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
         <v>35.7142857142857</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
         <v>30</v>
       </c>
-      <c r="D2" s="16" t="str">
+      <c r="D2" s="17" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
-      <c r="E2" s="16" t="str">
+      <c r="E2" s="17" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
         <v>71.4285714285714</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
         <v>55</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="17" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
-      <c r="E3" s="16" t="str">
+      <c r="E3" s="17" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
         <v>107.142857142857</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
         <v>80</v>
       </c>
-      <c r="D4" s="16" t="str">
+      <c r="D4" s="17" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
-      <c r="E4" s="16" t="str">
+      <c r="E4" s="17" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
         <v>142.857142857143</v>
       </c>
-      <c r="C5" s="16" t="str">
+      <c r="C5" s="17" t="str">
         <f aca="false">IF(スマホ!B30="","",スマホ!B30)</f>
         <v/>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
         <v>122.5</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
         <v>106.666666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
         <v>178.571428571429</v>
       </c>
-      <c r="C6" s="16" t="str">
+      <c r="C6" s="17" t="str">
         <f aca="false">IF(スマホ!B31="","",スマホ!B31)</f>
         <v/>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
         <v>165</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
         <v>133.333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
         <v>214.285714285714</v>
       </c>
-      <c r="C7" s="16" t="str">
+      <c r="C7" s="17" t="str">
         <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
         <v/>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
         <v>207.5</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
         <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A8/前提!$B$4</f>
         <v>250</v>
       </c>
-      <c r="C8" s="16" t="str">
+      <c r="C8" s="17" t="str">
         <f aca="false">IF(スマホ!B33="","",スマホ!B33)</f>
         <v/>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4)),"")</f>
         <v>250</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A8-ボード!$B$4)),"")</f>
         <v>186.666666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2766,7 +2772,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2779,7 +2785,7 @@
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <f aca="false">IF(COUNT(記録!C2:C8)=0,"",INDEX(記録!A2:A8,MATCH(9.99E+307,記録!C2:C8)))</f>
         <v>3</v>
       </c>
@@ -2788,7 +2794,7 @@
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <f aca="false">IF(B4="","",INDEX(記録!C2:C8,MATCH(9.99E+307,記録!C2:C8)))</f>
         <v>80</v>
       </c>
@@ -2797,7 +2803,7 @@
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <f aca="false">前提!B3</f>
         <v>250</v>
       </c>
@@ -2806,7 +2812,7 @@
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.32</v>
       </c>
@@ -2815,7 +2821,7 @@
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="19" t="str">
+      <c r="B8" s="20" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((B5-INDEX(記録!B2:B8,B4))*SIGN((前提!B3-前提!B2))&gt;=0,"計画どおり、または先行","計画より遅れ")))</f>
         <v>計画より遅れ</v>
       </c>
@@ -2824,7 +2830,7 @@
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>4</v>
       </c>
@@ -2833,7 +2839,7 @@
       <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,0,IF(B9&lt;=0,"",(前提!B3-B5)/B9)))</f>
         <v>42.5</v>
       </c>
@@ -2842,7 +2848,7 @@
       <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <f aca="false">IF(COUNT(記録!C2:C8)&lt;2,"",(B5-前提!B2)/B4)</f>
         <v>26.6666666666667</v>
       </c>
@@ -2851,7 +2857,7 @@
       <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B12" s="20" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,"達成済み",IF(B9&lt;=0,"期限を過ぎています（前提の見直しが必要）",IF(COUNT(記録!C2:C8)&lt;2,"記録が2か月分以上で表示",IF(B11*SIGN((前提!B3-前提!B2))&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）")))))))</f>
         <v>期限より遅れる（10か月目ごろ）</v>
       </c>
@@ -2860,7 +2866,7 @@
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="20" t="str">
+      <c r="B13" s="21" t="str">
         <f aca="false">IF(COUNTIF(記録!C2:C8,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(COUNT(記録!C2:C8)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK")))</f>
         <v>OK</v>
       </c>
@@ -2871,7 +2877,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2881,85 +2887,85 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="C20" s="19" t="str">
+      <c r="C20" s="20" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B20,"達成","未達成"))</f>
         <v>達成</v>
       </c>
-      <c r="D20" s="19" t="str">
+      <c r="D20" s="20" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B20,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B20-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>—</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="C21" s="19" t="str">
+      <c r="C21" s="20" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B21,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
-      <c r="D21" s="19" t="str">
+      <c r="D21" s="20" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B21,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B21-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>5か月目ごろ</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="C22" s="19" t="str">
+      <c r="C22" s="20" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B22,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
-      <c r="D22" s="19" t="str">
+      <c r="D22" s="20" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B22,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B22-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>8か月目ごろ</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="11" t="n">
         <v>250</v>
       </c>
-      <c r="C23" s="19" t="str">
+      <c r="C23" s="20" t="str">
         <f aca="false">IF(B$5="","",IF(B$5&gt;=B23,"達成","未達成"))</f>
         <v>未達成</v>
       </c>
-      <c r="D23" s="19" t="str">
+      <c r="D23" s="20" t="str">
         <f aca="false">IFERROR(IF(B$5="","",IF(B$5&gt;=B23,"—",IF(B$11="","記録が2か月分以上で表示",IF(B$11&lt;=0,"見込みなし",ROUNDUP(B$4+(B23-B$5)/B$11,0)&amp;"か月目ごろ")))),"")</f>
         <v>10か月目ごろ</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>60</v>
       </c>
     </row>
